--- a/data/trans_camb/IP22_R-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP22_R-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-12.18671396680219</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-13.70623173824756</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-5.67384731285668</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-10.92235641715747</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-9.058124550154755</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-12.35439678275345</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-18.62248629960864</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-20.89381839837719</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-11.54604289683748</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-18.79119580404204</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-13.30424980264007</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-17.14965322504152</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>-6.655823523156869</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-5.105748596355092</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.6498364860686634</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-2.347324419624227</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-4.94591631367822</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-5.932939687930364</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.4239839755297725</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.4768490208061736</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.2159009771651195</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.4156170043678397</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3288942355353239</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.4485795997687337</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.5664926548707095</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.6701094744891876</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.3947184278455448</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.6373615380192427</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4375171604319665</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5966874458869471</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>-0.2514762393001391</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-0.1676740426796512</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.02849829109797422</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0.09415617956132742</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.1885506101625525</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.2345603304406514</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-13.66689592070004</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-16.49006182501858</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-6.052937937555916</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-12.63230737306051</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-9.857104905846331</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-14.42610143469422</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-19.97207414617171</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-22.79853241008961</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-11.68950069160983</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-17.97446987542356</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-14.99034512228936</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-19.11585647720457</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>-6.762994518671227</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-8.951128442629265</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-0.09801525315714277</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-6.557338461940143</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-5.901605669540779</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-9.872410270809917</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.4327886476126113</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.5221896469913696</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.2608874246212901</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.5444645511949538</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3599022284655984</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.5267252508733885</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.5693734140893595</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.6629332836900694</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.4493390009440026</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.6932059563874117</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4977800755784098</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6473392797366718</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>-0.2332391348092346</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-0.3197438177898025</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-0.002922693520940121</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.3172539074890148</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.2307805505808247</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.3802199369396185</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-5.882319416729645</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-7.131756528102959</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-8.059146292902804</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-3.346188379969078</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-7.001928023418746</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-5.404784748457939</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-13.13698001613611</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-14.04099699030742</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-14.9929680727545</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-10.34982435532699</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-11.85213676867102</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-9.922185634828582</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>2.097500980897181</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.03760916944086666</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-0.8371315605940011</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.301788236502825</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-2.474938302207139</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-0.5258972976938445</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.2727874162117221</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.3307289690558643</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.3824407226178287</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.1587908514798553</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3283963966270198</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.2534890147402067</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.5093819031256897</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.5471306791711836</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.6072817558999445</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.4149975388330347</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.4975114994593025</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.4178261304103055</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.1332473633800675</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.006298760913570197</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-0.03059694468880104</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.2167176621106459</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-0.1270554922498187</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-0.02569472075613642</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-8.118273982087818</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-9.290926677191374</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-2.332142958017652</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-2.382188196248614</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-5.512281495218538</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-6.04653204610229</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-18.16592290052172</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-18.3502212478365</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-12.47124429802766</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-11.94064740820866</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-12.37644209219915</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-13.44042255080432</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>1.211841800006826</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-0.7104984456315451</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>7.593054434955122</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>6.915171075318955</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>2.121051768687241</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.3720045345908726</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.3166654651808948</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.3624065441355988</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.1082934721080023</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.1106173316260781</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.2318673418970479</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.254339934279694</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.5811606139046959</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.5980122950758705</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.4809958759224041</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.4389733956704279</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.4480356991671798</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.4664311108146756</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.08021608994959512</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>-0.03377496541156058</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.4423388823967914</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.453213124989103</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.1171794175304092</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.0247227915396612</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-10.75331242097689</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-12.50364256852246</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-5.84555767954838</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-8.091328248761712</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-8.357727826789981</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-10.35486016342938</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-14.34366372480343</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-16.41260626412939</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-9.437408404690268</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-11.55587360754801</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-10.56238150639238</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-12.91406589018896</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>-7.215016068905496</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-8.286076495005251</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-2.2884720815576</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-4.55213627180679</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-5.595163506830684</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-7.754996166548543</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.3891593753114219</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.4525033348414013</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.2476277942839043</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.3427624662875121</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.3256554410919651</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.4034728844792217</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.4874197930550621</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.5479645693260135</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.3643533717289496</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.4548927533013127</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.3966980354861328</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.4767632194870703</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>-0.2814205133228431</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.3224747645280929</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>-0.105793177600255</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0.2032900140253303</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.2336531290767991</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.3117681276894404</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
